--- a/dosc/lab03/Testcase_template.xlsx
+++ b/dosc/lab03/Testcase_template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="97">
   <si>
     <t>Use case ID/ Req. ID</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>เมธอด return ผลลัพธ์เป็น "VRIWZDUH"</t>
+  </si>
+  <si>
+    <t>การเลื่อนตำแหน่งผิด</t>
   </si>
   <si>
     <t>2. message เป็นตัวอักษร a-z จะให้ผลลัพธ์เป็น a-z</t>
@@ -590,8 +593,8 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -29003,7 +29006,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="20">
-        <v>25422.0</v>
+        <v>46241.0</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="19" t="s">
@@ -29020,8 +29023,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18">
-        <v>1.0</v>
+      <c r="A4" s="19">
+        <v>2.0</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>30</v>
@@ -29030,7 +29033,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="20">
-        <v>25423.0</v>
+        <v>46241.0</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="19" t="s">
@@ -30187,100 +30190,102 @@
       <c r="G9" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="37"/>
+      <c r="H9" s="36" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="37" t="s">
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="38" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11">
       <c r="A11" s="39"/>
       <c r="B11" s="39"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37" t="s">
-        <v>64</v>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38" t="s">
+        <v>65</v>
       </c>
       <c r="E11" s="39"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
     </row>
     <row r="12">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
     </row>
     <row r="13">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
     </row>
     <row r="14">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
     </row>
     <row r="15">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
     </row>
     <row r="17">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="18">
       <c r="A18" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -31341,7 +31346,7 @@
     </row>
     <row r="2" ht="24.0" customHeight="1">
       <c r="A2" s="43" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -31399,15 +31404,15 @@
     </row>
     <row r="4" ht="24.0" customHeight="1">
       <c r="A4" s="45" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" s="24" t="s">
         <v>36</v>
@@ -31435,18 +31440,18 @@
     </row>
     <row r="5" ht="24.0" customHeight="1">
       <c r="A5" s="45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="1"/>
@@ -31471,7 +31476,7 @@
     </row>
     <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="49"/>
       <c r="C6" s="11"/>
@@ -31532,20 +31537,20 @@
         <v>1</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="51" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="53"/>
       <c r="I8" s="53"/>
@@ -31571,10 +31576,10 @@
       <c r="A9" s="39"/>
       <c r="B9" s="39"/>
       <c r="C9" s="54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
@@ -31604,10 +31609,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" s="9">
         <v>3.0</v>
@@ -31619,7 +31624,7 @@
         <v>62</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -31642,24 +31647,24 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" ht="24.0" customHeight="1">
-      <c r="A11" s="38"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" s="9">
         <v>3.0</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -31682,24 +31687,24 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" ht="24.0" customHeight="1">
-      <c r="A12" s="38"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" s="13">
         <v>3.0</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -31724,22 +31729,22 @@
     <row r="13" ht="24.0" customHeight="1">
       <c r="A13" s="39"/>
       <c r="B13" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="13">
         <v>3.0</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
